--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -24821,6 +24821,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1064">
+      <c r="A1064" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1064" t="n">
+        <v>33825</v>
+      </c>
+      <c r="C1064" t="n">
+        <v>0.425000011920929</v>
+      </c>
+      <c r="D1064" t="n">
+        <v>0.400999993085861</v>
+      </c>
+      <c r="E1064" t="n">
+        <v>0.425000011920929</v>
+      </c>
+      <c r="F1064" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="G1064" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -24844,6 +24844,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1065">
+      <c r="A1065" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1065" t="n">
+        <v>24750</v>
+      </c>
+      <c r="C1065" t="n">
+        <v>0.404000014066696</v>
+      </c>
+      <c r="D1065" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1065" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="F1065" t="n">
+        <v>0.395000010728836</v>
+      </c>
+      <c r="G1065" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -24867,6 +24867,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1066">
+      <c r="A1066" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1066" t="n">
+        <v>15675</v>
+      </c>
+      <c r="C1066" t="n">
+        <v>0.395000010728836</v>
+      </c>
+      <c r="D1066" t="n">
+        <v>0.386999994516373</v>
+      </c>
+      <c r="E1066" t="n">
+        <v>0.395000010728836</v>
+      </c>
+      <c r="F1066" t="n">
+        <v>0.386999994516373</v>
+      </c>
+      <c r="G1066" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -24890,6 +24890,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1067">
+      <c r="A1067" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1067" t="n">
+        <v>33825</v>
+      </c>
+      <c r="C1067" t="n">
+        <v>0.395000010728836</v>
+      </c>
+      <c r="D1067" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1067" t="n">
+        <v>0.391000002622604</v>
+      </c>
+      <c r="F1067" t="n">
+        <v>0.388999998569489</v>
+      </c>
+      <c r="G1067" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -24731,22 +24731,22 @@
     </row>
     <row r="1060">
       <c r="A1060" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1060" t="n">
-        <v>140250</v>
+        <v>190575</v>
       </c>
       <c r="C1060" t="n">
-        <v>0.437000006437302</v>
+        <v>0.418999999761581</v>
       </c>
       <c r="D1060" t="n">
-        <v>0.400999993085861</v>
+        <v>0.388999998569489</v>
       </c>
       <c r="E1060" t="n">
-        <v>0.409999996423721</v>
+        <v>0.398000001907349</v>
       </c>
       <c r="F1060" t="n">
-        <v>0.416000008583069</v>
+        <v>0.40200001001358</v>
       </c>
       <c r="G1060" t="s">
         <v>7</v>
@@ -24754,22 +24754,22 @@
     </row>
     <row r="1061">
       <c r="A1061" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1061" t="n">
-        <v>701250</v>
+        <v>140250</v>
       </c>
       <c r="C1061" t="n">
-        <v>0.469999998807907</v>
+        <v>0.437000006437302</v>
       </c>
       <c r="D1061" t="n">
-        <v>0.425999999046326</v>
+        <v>0.400999993085861</v>
       </c>
       <c r="E1061" t="n">
-        <v>0.428999990224838</v>
+        <v>0.409999996423721</v>
       </c>
       <c r="F1061" t="n">
-        <v>0.430000007152557</v>
+        <v>0.416000008583069</v>
       </c>
       <c r="G1061" t="s">
         <v>7</v>
@@ -24777,22 +24777,22 @@
     </row>
     <row r="1062">
       <c r="A1062" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1062" t="n">
-        <v>186450</v>
+        <v>701250</v>
       </c>
       <c r="C1062" t="n">
-        <v>0.439999997615814</v>
+        <v>0.469999998807907</v>
       </c>
       <c r="D1062" t="n">
-        <v>0.397000014781952</v>
+        <v>0.425999999046326</v>
       </c>
       <c r="E1062" t="n">
-        <v>0.437999993562698</v>
+        <v>0.428999990224838</v>
       </c>
       <c r="F1062" t="n">
-        <v>0.416999995708466</v>
+        <v>0.430000007152557</v>
       </c>
       <c r="G1062" t="s">
         <v>7</v>
@@ -24800,22 +24800,22 @@
     </row>
     <row r="1063">
       <c r="A1063" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1063" t="n">
-        <v>21450</v>
+        <v>186450</v>
       </c>
       <c r="C1063" t="n">
-        <v>0.426999986171722</v>
+        <v>0.439999997615814</v>
       </c>
       <c r="D1063" t="n">
-        <v>0.402999997138977</v>
+        <v>0.397000014781952</v>
       </c>
       <c r="E1063" t="n">
-        <v>0.404000014066696</v>
+        <v>0.437999993562698</v>
       </c>
       <c r="F1063" t="n">
-        <v>0.426999986171722</v>
+        <v>0.416999995708466</v>
       </c>
       <c r="G1063" t="s">
         <v>7</v>
@@ -24823,22 +24823,22 @@
     </row>
     <row r="1064">
       <c r="A1064" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1064" t="n">
-        <v>33825</v>
+        <v>21450</v>
       </c>
       <c r="C1064" t="n">
-        <v>0.425000011920929</v>
+        <v>0.426999986171722</v>
       </c>
       <c r="D1064" t="n">
-        <v>0.400999993085861</v>
+        <v>0.402999997138977</v>
       </c>
       <c r="E1064" t="n">
-        <v>0.425000011920929</v>
+        <v>0.404000014066696</v>
       </c>
       <c r="F1064" t="n">
-        <v>0.409999996423721</v>
+        <v>0.426999986171722</v>
       </c>
       <c r="G1064" t="s">
         <v>7</v>
@@ -24846,22 +24846,22 @@
     </row>
     <row r="1065">
       <c r="A1065" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1065" t="n">
-        <v>24750</v>
+        <v>33825</v>
       </c>
       <c r="C1065" t="n">
-        <v>0.404000014066696</v>
+        <v>0.425000011920929</v>
       </c>
       <c r="D1065" t="n">
-        <v>0.384999990463257</v>
+        <v>0.400999993085861</v>
       </c>
       <c r="E1065" t="n">
-        <v>0.400000005960464</v>
+        <v>0.425000011920929</v>
       </c>
       <c r="F1065" t="n">
-        <v>0.395000010728836</v>
+        <v>0.409999996423721</v>
       </c>
       <c r="G1065" t="s">
         <v>7</v>
@@ -24869,22 +24869,22 @@
     </row>
     <row r="1066">
       <c r="A1066" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1066" t="n">
-        <v>15675</v>
+        <v>24750</v>
       </c>
       <c r="C1066" t="n">
+        <v>0.404000014066696</v>
+      </c>
+      <c r="D1066" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1066" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="F1066" t="n">
         <v>0.395000010728836</v>
-      </c>
-      <c r="D1066" t="n">
-        <v>0.386999994516373</v>
-      </c>
-      <c r="E1066" t="n">
-        <v>0.395000010728836</v>
-      </c>
-      <c r="F1066" t="n">
-        <v>0.386999994516373</v>
       </c>
       <c r="G1066" t="s">
         <v>7</v>
@@ -24892,24 +24892,47 @@
     </row>
     <row r="1067">
       <c r="A1067" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1067" t="n">
-        <v>33825</v>
+        <v>15675</v>
       </c>
       <c r="C1067" t="n">
         <v>0.395000010728836</v>
       </c>
       <c r="D1067" t="n">
+        <v>0.386999994516373</v>
+      </c>
+      <c r="E1067" t="n">
+        <v>0.395000010728836</v>
+      </c>
+      <c r="F1067" t="n">
+        <v>0.386999994516373</v>
+      </c>
+      <c r="G1067" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1068" t="n">
+        <v>12375</v>
+      </c>
+      <c r="C1068" t="n">
+        <v>0.39300000667572</v>
+      </c>
+      <c r="D1068" t="n">
         <v>0.384999990463257</v>
       </c>
-      <c r="E1067" t="n">
-        <v>0.391000002622604</v>
-      </c>
-      <c r="F1067" t="n">
-        <v>0.388999998569489</v>
-      </c>
-      <c r="G1067" t="s">
+      <c r="E1068" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="F1068" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="G1068" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -28195,6 +28195,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1071">
+      <c r="A1071" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1071" t="n">
+        <v>17325</v>
+      </c>
+      <c r="C1071" t="n">
+        <v>0.405000001192093</v>
+      </c>
+      <c r="D1071" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="E1071" t="n">
+        <v>0.405000001192093</v>
+      </c>
+      <c r="F1071" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="G1071" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="H1071" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -28221,6 +28221,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1072">
+      <c r="A1072" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1072" t="n">
+        <v>28050</v>
+      </c>
+      <c r="C1072" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="D1072" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1072" t="n">
+        <v>0.391000002622604</v>
+      </c>
+      <c r="F1072" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="G1072" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="H1072" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -28247,6 +28247,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1073">
+      <c r="A1073" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1073" t="n">
+        <v>103950</v>
+      </c>
+      <c r="C1073" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="D1073" t="n">
+        <v>0.370000004768372</v>
+      </c>
+      <c r="E1073" t="n">
+        <v>0.386000007390976</v>
+      </c>
+      <c r="F1073" t="n">
+        <v>0.379000008106232</v>
+      </c>
+      <c r="G1073" t="n">
+        <v>0.379000008106232</v>
+      </c>
+      <c r="H1073" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -28273,6 +28273,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1074">
+      <c r="A1074" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1074" t="n">
+        <v>26400</v>
+      </c>
+      <c r="C1074" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="D1074" t="n">
+        <v>0.375999987125397</v>
+      </c>
+      <c r="E1074" t="n">
+        <v>0.375999987125397</v>
+      </c>
+      <c r="F1074" t="n">
+        <v>0.379000008106232</v>
+      </c>
+      <c r="G1074" t="n">
+        <v>0.379000008106232</v>
+      </c>
+      <c r="H1074" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -25120,6 +25120,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1077">
+      <c r="A1077" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1077" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="D1077" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1077" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="F1077" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="G1077" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -25143,6 +25143,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1078">
+      <c r="A1078" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1078" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="D1078" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1078" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="F1078" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="G1078" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -25166,6 +25166,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1079">
+      <c r="A1079" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B1079" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1079" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="D1079" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1079" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="F1079" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="G1079" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -25189,6 +25189,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1080">
+      <c r="A1080" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B1080" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1080" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="D1080" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1080" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="F1080" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="G1080" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -25212,6 +25212,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1081">
+      <c r="A1081" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1081" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1081" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="D1081" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1081" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="F1081" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="G1081" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -25235,6 +25235,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1082">
+      <c r="A1082" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1082" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1082" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="D1082" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1082" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="F1082" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="G1082" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -25258,6 +25258,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1083">
+      <c r="A1083" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1083" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1083" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="D1083" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1083" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="F1083" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="G1083" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -25304,6 +25304,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1085">
+      <c r="A1085" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1085" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="D1085" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1085" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="F1085" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="G1085" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -25327,6 +25327,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1086">
+      <c r="A1086" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B1086" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1086" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="D1086" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1086" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="F1086" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="G1086" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -25350,6 +25350,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1087">
+      <c r="A1087" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B1087" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1087" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="D1087" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1087" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="F1087" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="G1087" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -25373,6 +25373,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1088">
+      <c r="A1088" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1088" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1088" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="D1088" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1088" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="G1088" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -31959,6 +31959,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1090">
+      <c r="A1090" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1090" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1090" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="D1090" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1090" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="F1090" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="G1090" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="H1090" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1090" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -31988,6 +31988,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1091">
+      <c r="A1091" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1091" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1091" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="D1091" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1091" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="G1091" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="H1091" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1091" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -32017,6 +32017,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1092">
+      <c r="A1092" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1092" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1092" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="D1092" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1092" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="F1092" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="G1092" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="H1092" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1092" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -32046,6 +32046,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1093">
+      <c r="A1093" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1093" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1093" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="D1093" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1093" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="F1093" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="G1093" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="H1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1093" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -32075,6 +32075,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1094">
+      <c r="A1094" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1094" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1094" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="D1094" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1094" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="G1094" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="H1094" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1094" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -32104,6 +32104,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1095">
+      <c r="A1095" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1095" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1095" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="D1095" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1095" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="F1095" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="G1095" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="H1095" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1095" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -32133,6 +32133,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1096">
+      <c r="A1096" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1096" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1096" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="D1096" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1096" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="F1096" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="G1096" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="H1096" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1096" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -32162,6 +32162,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1097">
+      <c r="A1097" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1097" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1097" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="D1097" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1097" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="F1097" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="G1097" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="H1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1097" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/S3D.MI.xlsx
+++ b/data/S3D.MI.xlsx
@@ -32191,6 +32191,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1098">
+      <c r="A1098" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1098" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1098" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="D1098" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="E1098" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="F1098" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="G1098" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="H1098" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1098" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
